--- a/ProyectoTasasMercantil/cortes/2026-05/output_v10/producto_b_escenarios_mayo2026.xlsx
+++ b/ProyectoTasasMercantil/cortes/2026-05/output_v10/producto_b_escenarios_mayo2026.xlsx
@@ -432,15 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>Ret mean</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,7 +489,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Esperado</t>
+          <t>Esperado (HDI 50%)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -498,6 +504,11 @@
       <c r="F2" s="3" t="n">
         <v>0.005772672870597376</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HDI 50% optimizado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +533,11 @@
       <c r="F3" s="3" t="n">
         <v>0.01801305443111404</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,16 +551,21 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1942</v>
+        <v>0.2442</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.01185558502190687</v>
+        <v>-0.01541670032941078</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>-0.001208483537887112</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.006416149545902343</v>
+        <v>-0.007850682218503295</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -555,20 +576,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Riesgo (cola)</t>
+          <t>Riesgo (cola izq)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>-0.0306409942185107</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.01185818788588569</v>
+        <v>-0.01542619313726092</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.01626611097730335</v>
+        <v>-0.01910981483572129</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cutoff P5 fijo</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -579,7 +605,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Esperado</t>
+          <t>Esperado (HDI 50%)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -594,6 +620,11 @@
       <c r="F6" s="3" t="n">
         <v>0.01464464398109307</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HDI 50% optimizado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,6 +649,11 @@
       <c r="F7" s="3" t="n">
         <v>0.02874575246560194</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,16 +667,21 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.1138</v>
+        <v>0.1638</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.002773997443424957</v>
+        <v>-0.001376975976022239</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0.007603630096241513</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.005358100461866799</v>
+        <v>0.003986609486042866</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -651,20 +692,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Riesgo (cola)</t>
+          <t>Riesgo (cola izq)</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>-0.02679884415400458</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.002768960445828664</v>
+        <v>-0.001421035790166681</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.002387696138595605</v>
+        <v>-0.0056404883022588</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cutoff P5 fijo</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -675,7 +721,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Esperado</t>
+          <t>Esperado (HDI 50%)</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -690,6 +736,11 @@
       <c r="F10" s="3" t="n">
         <v>0.02964140538684749</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HDI 50% optimizado</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -714,6 +765,11 @@
       <c r="F11" s="3" t="n">
         <v>0.04891875059949964</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -727,16 +783,21 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.1558</v>
+        <v>0.2058</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.007607870162252621</v>
+        <v>0.0007639792212185508</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0.0185849285017154</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.01337976667372472</v>
+        <v>0.01119143341760183</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -747,20 +808,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Riesgo (cola)</t>
+          <t>Riesgo (cola izq)</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0.02803776518393729</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.007590991667898507</v>
+        <v>0.0007564029599216125</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.0004959869075443977</v>
+        <v>-0.005364560806611701</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cutoff P5 fijo</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -771,7 +837,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Esperado</t>
+          <t>Esperado (HDI 50%)</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -786,6 +852,11 @@
       <c r="F14" s="3" t="n">
         <v>0.06113227196816239</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HDI 50% optimizado</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -810,6 +881,11 @@
       <c r="F15" s="3" t="n">
         <v>0.08777504417519796</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -823,16 +899,21 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.1858</v>
+        <v>0.2358</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.02609121809255123</v>
+        <v>0.01565677124436401</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.04483700446771255</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.03682390624573902</v>
+        <v>0.03358135493131743</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Empírica</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -843,20 +924,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Riesgo (cola)</t>
+          <t>Riesgo (cola izq)</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.0781602419035767</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0260677450810763</v>
+        <v>0.01556336947901941</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.001500127875426509</v>
+        <v>-0.01853177849607374</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cutoff P5 fijo</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -870,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -883,6 +969,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -923,15 +1011,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Bajista prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Bajista mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Alcista prob</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Alcista mean</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Riesgo mean</t>
         </is>
@@ -961,14 +1059,20 @@
       <c r="G2" s="3" t="n">
         <v>0.00338484553819709</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0.002913097477163078</v>
+      <c r="H2" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>0.002900330905725409</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>0.003662811521080745</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0.002770058659442741</v>
+      <c r="L2" s="3" t="n">
+        <v>0.002665319556035414</v>
       </c>
     </row>
     <row r="3">
@@ -995,7 +1099,7 @@
       <c r="G3" s="3" t="n">
         <v>0.009927019179082754</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>-0.03396909054165839</v>
       </c>
     </row>
@@ -1023,7 +1127,7 @@
       <c r="G4" s="3" t="n">
         <v>0.007697716726516349</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>-0.01607402997741589</v>
       </c>
     </row>
@@ -1051,11 +1155,20 @@
       <c r="G5" s="3" t="n">
         <v>0.002687863012728418</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>0.06666666666666667</v>
+      </c>
       <c r="I5" s="3" t="n">
+        <v>-0.007393714959932134</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>0.01909045657826748</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>-0.01417066920263284</v>
+      <c r="L5" s="3" t="n">
+        <v>-0.02094762344533356</v>
       </c>
     </row>
     <row r="6">
@@ -1082,14 +1195,20 @@
       <c r="G6" s="3" t="n">
         <v>0.01404350230934821</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.01342586690496963</v>
+      <c r="H6" s="2" t="n">
+        <v>0.2333333333333333</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>-0.01503769956345937</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>0.03471279013681823</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>-0.04274944187782651</v>
+      <c r="L6" s="3" t="n">
+        <v>-0.05176981505954086</v>
       </c>
     </row>
     <row r="7">
@@ -1116,14 +1235,20 @@
       <c r="G7" s="3" t="n">
         <v>0.01866028568392691</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.01423004177492927</v>
+      <c r="H7" s="2" t="n">
+        <v>0.1666666666666667</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>-0.01887162961529181</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>0.05487347895446605</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>-0.06639271018819547</v>
+      <c r="L7" s="3" t="n">
+        <v>-0.08087007479392219</v>
       </c>
     </row>
   </sheetData>
@@ -1137,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1150,6 +1275,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1190,15 +1317,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Bajista prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Bajista mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Alcista prob</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Alcista mean</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Riesgo mean</t>
         </is>
@@ -1228,7 +1365,7 @@
       <c r="G2" s="3" t="n">
         <v>0.01007217063316786</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="L2" s="3" t="n">
         <v>0.009178824520923888</v>
       </c>
     </row>
@@ -1256,8 +1393,14 @@
       <c r="G3" s="3" t="n">
         <v>0.005910918927909691</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="J3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.03834096612852611</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>-0.0008383108528250993</v>
       </c>
     </row>
     <row r="4">
@@ -1284,14 +1427,20 @@
       <c r="G4" s="3" t="n">
         <v>0.01559018620461864</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.009859553349121209</v>
+      <c r="H4" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>-0.01345592117508749</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0.04831376747808549</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>-0.04469041964952482</v>
+      <c r="L4" s="3" t="n">
+        <v>-0.06513581464606331</v>
       </c>
     </row>
     <row r="5">
@@ -1318,14 +1467,20 @@
       <c r="G5" s="3" t="n">
         <v>0.007063960420905367</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.02352366924431487</v>
+      <c r="H5" s="2" t="n">
+        <v>0.15</v>
       </c>
       <c r="I5" s="3" t="n">
+        <v>-0.02908114208387905</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>0.05052724161587083</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>-0.06457703861957635</v>
+      <c r="L5" s="3" t="n">
+        <v>-0.0889579894761453</v>
       </c>
     </row>
     <row r="6">
@@ -1352,7 +1507,7 @@
       <c r="G6" s="3" t="n">
         <v>0.0390838173685232</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>0.01122085139923585</v>
       </c>
     </row>
@@ -1380,14 +1535,20 @@
       <c r="G7" s="3" t="n">
         <v>0.05106658800155846</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.003828435813042642</v>
+      <c r="H7" s="2" t="n">
+        <v>0.325</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>-0.01229335021110386</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>0.1122551005704433</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>-0.06860581970002905</v>
+      <c r="L7" s="3" t="n">
+        <v>-0.07836125999961754</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1414,6 +1575,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1454,15 +1617,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Bajista prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Bajista mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Alcista prob</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Alcista mean</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Riesgo mean</t>
         </is>
@@ -1492,14 +1665,20 @@
       <c r="G2" s="3" t="n">
         <v>0.0228915833557168</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0.01339854905806145</v>
+      <c r="H2" s="2" t="n">
+        <v>0.375</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>0.01277711522938069</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>0.02614411144816059</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0.008333249709447488</v>
+      <c r="L2" s="3" t="n">
+        <v>0.007928704075939218</v>
       </c>
     </row>
     <row r="3">
@@ -1526,14 +1705,20 @@
       <c r="G3" s="3" t="n">
         <v>0.02232472235026827</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.009245556605475824</v>
+      <c r="H3" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="I3" s="3" t="n">
+        <v>-0.01652538183745085</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.05109164492867588</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>-0.03431665319051761</v>
+      <c r="L3" s="3" t="n">
+        <v>-0.03754827407963433</v>
       </c>
     </row>
     <row r="4">
@@ -1560,14 +1745,20 @@
       <c r="G4" s="3" t="n">
         <v>0.04371207893236804</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>0.001510915703498805</v>
+      <c r="H4" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>-0.002991007604325399</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0.07425156267500037</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>-0.01999240288770823</v>
+      <c r="L4" s="3" t="n">
+        <v>-0.02798995155544265</v>
       </c>
     </row>
     <row r="5">
@@ -1594,13 +1785,19 @@
       <c r="G5" s="3" t="n">
         <v>0.04295310694208949</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>0.0281463227515063</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="J5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>0.05949055292958431</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>-0.000448319158765597</v>
       </c>
     </row>
@@ -1628,14 +1825,20 @@
       <c r="G6" s="3" t="n">
         <v>0.05047101223514164</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>0.01198966270193896</v>
+      <c r="H6" s="2" t="n">
+        <v>0.2333333333333333</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>0.007160748161530623</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>0.0879911546848903</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>-0.02391192511651908</v>
+      <c r="L6" s="3" t="n">
+        <v>-0.02496151813431893</v>
       </c>
     </row>
     <row r="7">
@@ -1662,14 +1865,20 @@
       <c r="G7" s="3" t="n">
         <v>0.05850163654014513</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.02110504580299551</v>
+      <c r="H7" s="2" t="n">
+        <v>0.15</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>-0.02580209803863598</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>0.1631944123557101</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>-0.06416693986294296</v>
+      <c r="L7" s="3" t="n">
+        <v>-0.09313767721596899</v>
       </c>
     </row>
   </sheetData>
@@ -1683,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1696,6 +1905,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1736,15 +1947,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Bajista prob</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Bajista mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Alcista prob</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Alcista mean</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Riesgo mean</t>
         </is>
@@ -1774,14 +1995,20 @@
       <c r="G2" s="3" t="n">
         <v>0.04526662117053176</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0.02450026632857565</v>
+      <c r="H2" s="2" t="n">
+        <v>0.375</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>0.02335979064436185</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>0.05206630160008192</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0.01155152090605692</v>
+      <c r="L2" s="3" t="n">
+        <v>0.007156343115141609</v>
       </c>
     </row>
     <row r="3">
@@ -1808,14 +2035,20 @@
       <c r="G3" s="3" t="n">
         <v>0.04728297753125116</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.009547445739212164</v>
+      <c r="H3" s="2" t="n">
+        <v>0.325</v>
       </c>
       <c r="I3" s="3" t="n">
+        <v>-0.0141769296448601</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.08880627928401205</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>-0.08619515400129173</v>
+      <c r="L3" s="3" t="n">
+        <v>-0.1327512168766597</v>
       </c>
     </row>
     <row r="4">
@@ -1842,14 +2075,20 @@
       <c r="G4" s="3" t="n">
         <v>0.0912424218387632</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>0.05893206334831302</v>
+      <c r="H4" s="2" t="n">
+        <v>0.2666666666666667</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>0.05381530723562744</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0.1501058839789083</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>0.03368198626692925</v>
+      <c r="L4" s="3" t="n">
+        <v>0.02889893363628779</v>
       </c>
     </row>
     <row r="5">
@@ -1876,14 +2115,20 @@
       <c r="G5" s="3" t="n">
         <v>0.06464058138235471</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>0.02543251797625046</v>
+      <c r="H5" s="2" t="n">
+        <v>0.2666666666666667</v>
       </c>
       <c r="I5" s="3" t="n">
+        <v>0.02311285225272031</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>0.1336357849719267</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>-0.01401512051223541</v>
+      <c r="L5" s="3" t="n">
+        <v>-0.02446027686235776</v>
       </c>
     </row>
     <row r="6">
@@ -1910,7 +2155,7 @@
       <c r="G6" s="3" t="n">
         <v>0.1185578747202815</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>0.0871742155445874</v>
       </c>
     </row>
@@ -1938,14 +2183,20 @@
       <c r="G7" s="3" t="n">
         <v>0.1659865730774817</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>0.04756203564432495</v>
+      <c r="H7" s="2" t="n">
+        <v>0.325</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>0.03012232431155389</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>0.2515001746155663</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>-0.09183145149535374</v>
+      <c r="L7" s="3" t="n">
+        <v>-0.1178668149720205</v>
       </c>
     </row>
   </sheetData>
